--- a/data/trans_dic/IP37-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han trabajado anteriormente</t>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49,58; 69,28</t>
+          <t>48,74; 68,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,39; 86,14</t>
+          <t>70,01; 85,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,11; 80,93</t>
+          <t>63,13; 80,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,83; 75,94</t>
+          <t>52,88; 75,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,96; 74,29</t>
+          <t>57,06; 75,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,74; 80,26</t>
+          <t>64,68; 80,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,9; 81,98</t>
+          <t>65,36; 82,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,91; 89,14</t>
+          <t>64,56; 89,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,83; 69,69</t>
+          <t>56,81; 69,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,96; 80,79</t>
+          <t>69,62; 80,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,29; 79,04</t>
+          <t>67,45; 79,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,66; 79,88</t>
+          <t>63,36; 80,04</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,1; 64,14</t>
+          <t>48,83; 64,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,05; 83,47</t>
+          <t>71,84; 83,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75,51; 86,88</t>
+          <t>74,44; 86,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,43; 84,28</t>
+          <t>62,63; 84,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,62; 71,94</t>
+          <t>56,32; 72,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,55; 84,86</t>
+          <t>73,61; 85,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,39; 75,12</t>
+          <t>61,1; 74,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>56,84; 76,78</t>
+          <t>58,19; 76,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,69; 65,65</t>
+          <t>55,04; 65,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,71; 83,13</t>
+          <t>74,83; 83,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,75; 78,89</t>
+          <t>69,81; 78,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>62,69; 78,24</t>
+          <t>63,2; 78,01</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,38; 72,17</t>
+          <t>53,32; 72,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,13; 80,16</t>
+          <t>64,58; 80,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,37; 77,51</t>
+          <t>61,69; 77,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,41; 89,91</t>
+          <t>59,61; 90,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,48; 72,13</t>
+          <t>52,64; 72,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,52; 74,27</t>
+          <t>58,91; 73,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,32; 81,68</t>
+          <t>65,52; 80,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59,71; 80,86</t>
+          <t>60,17; 80,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55,99; 69,32</t>
+          <t>56,7; 69,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,61; 75,03</t>
+          <t>63,79; 75,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,26; 77,64</t>
+          <t>65,72; 77,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64,29; 84,21</t>
+          <t>64,94; 85,19</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,39; 75,23</t>
+          <t>56,64; 75,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>70,65; 84,35</t>
+          <t>69,49; 84,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,11; 85,59</t>
+          <t>71,63; 85,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,52; 71,91</t>
+          <t>48,04; 71,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,31; 69,22</t>
+          <t>49,85; 68,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,23; 79,69</t>
+          <t>63,8; 79,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,24; 84,74</t>
+          <t>70,32; 84,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,74; 75,38</t>
+          <t>54,05; 75,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,06; 69,67</t>
+          <t>55,91; 69,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,01; 79,4</t>
+          <t>69,46; 80,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,73; 84,02</t>
+          <t>73,05; 83,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,52; 70,79</t>
+          <t>54,73; 70,72</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,86; 66,29</t>
+          <t>56,54; 65,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,46; 80,34</t>
+          <t>73,19; 80,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,36; 79,79</t>
+          <t>72,55; 79,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,64; 79,49</t>
+          <t>63,07; 79,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,76; 67,42</t>
+          <t>59,07; 67,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,75; 76,96</t>
+          <t>69,99; 76,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,34; 76,82</t>
+          <t>69,66; 77,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,93; 75,68</t>
+          <t>63,54; 75,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>58,98; 65,36</t>
+          <t>59,08; 65,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,56; 77,35</t>
+          <t>72,26; 77,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,04; 77,25</t>
+          <t>72,01; 77,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,78; 75,57</t>
+          <t>65,86; 75,95</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han trabajado anteriormente (tasa de respuesta: 99,71%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>41942</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64648</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56029</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32463</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>51430</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67562</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60169</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>38249</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>93372</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132210</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>116197</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>70711</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>34433; 48585</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>57581; 70381</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48907; 62384</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>26276; 37270</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>44037; 58034</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>59754; 74151</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>52766; 66340</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>31253; 43253</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>83975; 102338</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>121588; 141228</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>106701; 125330</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>62155; 78518</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>49845</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91857</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89556</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48068</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65410</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100418</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83288</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>54862</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>115255</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>192275</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>172845</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>102930</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>43372; 56936</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>84700; 98624</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>81858; 95232</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>40283; 54299</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>57211; 73369</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>92716; 107581</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>74420; 91238</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>46958; 61986</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>104791; 125491</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>182481; 203114</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>161782; 182476</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>91649; 113131</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>41880</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60542</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54686</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69258</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61785</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58604</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46238</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>84383</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122327</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>113291</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>115495</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>35153; 47823</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53373; 66277</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>48043; 60685</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55473; 83838</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>35653; 48786</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>54561; 68366</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>52124; 64414</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>39160; 52709</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>75784; 92433</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>111798; 131477</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>103462; 122202</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>102708; 134729</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>50634</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82508</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>76542</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30668</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>41657</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74458</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66415</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>40617</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>92291</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156965</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>142957</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>71285</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>43096; 57394</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>73870; 89361</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69496; 82640</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24298; 35968</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>35124; 48091</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>66185; 81966</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>59605; 71729</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>33630; 46868</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>81943; 102318</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>145897; 168260</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>132791; 152452</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>61730; 79772</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>184301</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>299556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>276814</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>180457</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>179964</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>385300</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>603778</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>545289</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>360421</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>170456; 197088</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>284784; 312239</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>262856; 288726</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>162495; 204839</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>187220; 214065</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>290227; 317646</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>255559; 283291</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>162932; 192773</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>365387; 404206</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>580782; 623064</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>525049; 563719</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>338564; 390416</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP37-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,74; 68,77</t>
+          <t>48,81; 67,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,01; 85,57</t>
+          <t>69,61; 85,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,13; 80,53</t>
+          <t>63,45; 80,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,88; 75,01</t>
+          <t>53,29; 75,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,06; 75,2</t>
+          <t>58,01; 74,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,68; 80,26</t>
+          <t>65,32; 80,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,36; 82,18</t>
+          <t>65,86; 81,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>64,56; 89,34</t>
+          <t>65,45; 89,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,81; 69,23</t>
+          <t>56,53; 68,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,62; 80,87</t>
+          <t>69,2; 80,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,45; 79,22</t>
+          <t>66,89; 79,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>63,36; 80,04</t>
+          <t>62,85; 80,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,83; 64,11</t>
+          <t>48,23; 64,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,84; 83,65</t>
+          <t>71,49; 83,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,44; 86,61</t>
+          <t>74,95; 86,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,63; 84,42</t>
+          <t>63,66; 85,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,32; 72,23</t>
+          <t>56,51; 71,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,61; 85,42</t>
+          <t>73,57; 85,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,1; 74,91</t>
+          <t>61,54; 74,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,19; 76,81</t>
+          <t>58,64; 77,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55,04; 65,91</t>
+          <t>54,35; 65,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,83; 83,3</t>
+          <t>74,91; 83,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,81; 78,74</t>
+          <t>69,5; 78,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,2; 78,01</t>
+          <t>63,11; 78,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,32; 72,53</t>
+          <t>54,1; 72,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,58; 80,19</t>
+          <t>65,37; 80,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,69; 77,93</t>
+          <t>60,91; 77,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,61; 90,09</t>
+          <t>60,78; 89,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52,64; 72,03</t>
+          <t>54,1; 71,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,91; 73,82</t>
+          <t>59,3; 74,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,52; 80,97</t>
+          <t>64,33; 80,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>60,17; 80,98</t>
+          <t>58,64; 79,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,7; 69,16</t>
+          <t>56,67; 69,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,79; 75,02</t>
+          <t>64,2; 75,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65,72; 77,62</t>
+          <t>65,71; 77,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64,94; 85,19</t>
+          <t>64,32; 86,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,64; 75,43</t>
+          <t>55,27; 74,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,49; 84,06</t>
+          <t>69,93; 84,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,63; 85,18</t>
+          <t>71,53; 85,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,04; 71,12</t>
+          <t>48,31; 71,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,85; 68,25</t>
+          <t>49,61; 68,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,8; 79,01</t>
+          <t>63,77; 79,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 84,62</t>
+          <t>69,27; 85,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>54,05; 75,32</t>
+          <t>53,1; 74,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>55,91; 69,82</t>
+          <t>56,61; 69,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,46; 80,11</t>
+          <t>69,37; 79,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>73,05; 83,86</t>
+          <t>72,32; 83,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,73; 70,72</t>
+          <t>54,49; 70,25</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,54; 65,37</t>
+          <t>56,86; 65,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,19; 80,25</t>
+          <t>73,15; 80,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,55; 79,69</t>
+          <t>72,64; 79,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,07; 79,5</t>
+          <t>63,53; 79,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,07; 67,54</t>
+          <t>59,33; 68,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,99; 76,6</t>
+          <t>69,4; 76,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,66; 77,22</t>
+          <t>69,4; 77,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,54; 75,18</t>
+          <t>64,27; 75,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,08; 65,36</t>
+          <t>59,25; 65,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,26; 77,52</t>
+          <t>72,49; 77,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,01; 77,31</t>
+          <t>72,23; 77,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,86; 75,95</t>
+          <t>65,95; 75,52</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34433; 48585</t>
+          <t>34488; 47858</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57581; 70381</t>
+          <t>57253; 70672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48907; 62384</t>
+          <t>49151; 62331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26276; 37270</t>
+          <t>26475; 37334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44037; 58034</t>
+          <t>44772; 57532</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59754; 74151</t>
+          <t>60345; 73971</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52766; 66340</t>
+          <t>53167; 66009</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31253; 43253</t>
+          <t>31686; 43476</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83975; 102338</t>
+          <t>83565; 101284</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121588; 141228</t>
+          <t>120842; 140844</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>106701; 125330</t>
+          <t>105818; 126188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62155; 78518</t>
+          <t>61657; 78759</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43372; 56936</t>
+          <t>42837; 57049</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84700; 98624</t>
+          <t>84282; 98901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81858; 95232</t>
+          <t>82414; 95323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40283; 54299</t>
+          <t>40945; 54779</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57211; 73369</t>
+          <t>57399; 72638</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92716; 107581</t>
+          <t>92659; 107506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74420; 91238</t>
+          <t>74959; 91335</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46958; 61986</t>
+          <t>47325; 62850</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>104791; 125491</t>
+          <t>103475; 125600</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182481; 203114</t>
+          <t>182667; 203247</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161782; 182476</t>
+          <t>161066; 182803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91649; 113131</t>
+          <t>91529; 113288</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35153; 47823</t>
+          <t>35670; 48125</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53373; 66277</t>
+          <t>54030; 66245</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48043; 60685</t>
+          <t>47431; 60473</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55473; 83838</t>
+          <t>56562; 83463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35653; 48786</t>
+          <t>36637; 48652</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54561; 68366</t>
+          <t>54916; 68838</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52124; 64414</t>
+          <t>51173; 63914</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39160; 52709</t>
+          <t>38167; 51950</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75784; 92433</t>
+          <t>75751; 92591</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>111798; 131477</t>
+          <t>112514; 131685</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103462; 122202</t>
+          <t>103453; 121575</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>102708; 134729</t>
+          <t>101726; 136339</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43096; 57394</t>
+          <t>42056; 57011</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73870; 89361</t>
+          <t>74334; 89584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69496; 82640</t>
+          <t>69399; 83086</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24298; 35968</t>
+          <t>24433; 36307</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35124; 48091</t>
+          <t>34954; 48111</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66185; 81966</t>
+          <t>66157; 82044</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59605; 71729</t>
+          <t>58712; 72248</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33630; 46868</t>
+          <t>33043; 46564</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81943; 102318</t>
+          <t>82965; 101613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>145897; 168260</t>
+          <t>145715; 166773</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>132791; 152452</t>
+          <t>131472; 151145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61730; 79772</t>
+          <t>61466; 79238</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>170456; 197088</t>
+          <t>171440; 198509</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>284784; 312239</t>
+          <t>284619; 312540</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>262856; 288726</t>
+          <t>263178; 289108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162495; 204839</t>
+          <t>163670; 205255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>187220; 214065</t>
+          <t>188033; 215929</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>290227; 317646</t>
+          <t>287798; 318138</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>255559; 283291</t>
+          <t>254604; 282717</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162932; 192773</t>
+          <t>164795; 193078</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>365387; 404206</t>
+          <t>366403; 403945</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>580782; 623064</t>
+          <t>582699; 623538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>525049; 563719</t>
+          <t>526669; 564503</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>338564; 390416</t>
+          <t>339051; 388210</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP37-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP37-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>73,13%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>76,33%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>59,36%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78,6%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>72,32%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>73,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,53%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,81; 67,74</t>
+          <t>56,96; 74,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,61; 85,92</t>
+          <t>65,74; 80,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,45; 80,46</t>
+          <t>64,9; 81,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,29; 75,14</t>
+          <t>59,99; 86,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,01; 74,55</t>
+          <t>49,58; 69,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,32; 80,07</t>
+          <t>70,39; 86,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,86; 81,77</t>
+          <t>64,11; 80,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,45; 89,8</t>
+          <t>50,75; 75,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56,53; 68,51</t>
+          <t>56,83; 69,69</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,2; 80,65</t>
+          <t>69,96; 80,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,89; 79,77</t>
+          <t>67,29; 79,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,85; 80,29</t>
+          <t>60,7; 77,07</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>64,4%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>79,73%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>67,49%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>56,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>77,91%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>81,44%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,23; 64,23</t>
+          <t>56,62; 71,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>71,49; 83,89</t>
+          <t>73,55; 84,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,95; 86,69</t>
+          <t>61,39; 75,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,66; 85,16</t>
+          <t>56,24; 76,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,51; 71,51</t>
+          <t>48,1; 64,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,57; 85,36</t>
+          <t>72,05; 83,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,54; 74,99</t>
+          <t>75,51; 86,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,64; 77,88</t>
+          <t>60,78; 82,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54,35; 65,97</t>
+          <t>54,69; 65,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,91; 83,35</t>
+          <t>74,71; 83,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69,5; 78,88</t>
+          <t>69,75; 78,89</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,11; 78,12</t>
+          <t>61,31; 77,4</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62,76%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>63,52%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>73,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>70,22%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74,42%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,1; 72,99</t>
+          <t>53,48; 72,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,37; 80,15</t>
+          <t>58,52; 74,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,91; 77,65</t>
+          <t>65,32; 81,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 89,69</t>
+          <t>59,13; 80,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,1; 71,84</t>
+          <t>54,38; 72,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>59,3; 74,33</t>
+          <t>64,13; 80,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,33; 80,34</t>
+          <t>61,37; 77,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,64; 79,82</t>
+          <t>48,43; 71,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,67; 69,27</t>
+          <t>55,99; 69,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,2; 75,14</t>
+          <t>63,61; 75,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65,71; 77,23</t>
+          <t>66,26; 77,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64,32; 86,21</t>
+          <t>57,99; 73,1</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59,12%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>78,35%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>66,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>77,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>78,89%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60,64%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,35%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55,27; 74,93</t>
+          <t>49,31; 69,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,93; 84,27</t>
+          <t>64,23; 79,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,53; 85,63</t>
+          <t>69,24; 84,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,31; 71,79</t>
+          <t>54,59; 74,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,61; 68,28</t>
+          <t>57,39; 75,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,77; 79,08</t>
+          <t>70,65; 84,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,27; 85,24</t>
+          <t>71,11; 85,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>53,1; 74,83</t>
+          <t>49,31; 72,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56,61; 69,34</t>
+          <t>56,06; 69,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,37; 79,4</t>
+          <t>69,01; 79,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72,32; 83,14</t>
+          <t>72,73; 84,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,49; 70,25</t>
+          <t>55,09; 70,6</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>73,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69,11%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>61,13%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>76,99%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>76,4%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>70,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>56,86; 65,84</t>
+          <t>58,76; 67,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>73,15; 80,32</t>
+          <t>69,75; 76,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,64; 79,79</t>
+          <t>69,34; 76,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,53; 79,67</t>
+          <t>63,97; 74,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,33; 68,13</t>
+          <t>56,86; 66,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 76,72</t>
+          <t>73,46; 80,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,4; 77,07</t>
+          <t>72,36; 79,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,27; 75,3</t>
+          <t>58,93; 69,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59,25; 65,32</t>
+          <t>58,98; 65,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,49; 77,57</t>
+          <t>72,56; 77,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72,23; 77,42</t>
+          <t>72,04; 77,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>65,95; 75,52</t>
+          <t>63,26; 71,21</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>51430</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67562</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>60169</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31064</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>41942</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>64648</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>56029</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32463</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>51430</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>67562</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60169</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>33679</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>64742</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34488; 47858</t>
+          <t>43961; 57331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57253; 70672</t>
+          <t>60738; 74154</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49151; 62331</t>
+          <t>52390; 66185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26475; 37334</t>
+          <t>24412; 35215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>44772; 57532</t>
+          <t>35032; 48945</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60345; 73971</t>
+          <t>57896; 70847</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53167; 66009</t>
+          <t>49665; 62699</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31686; 43476</t>
+          <t>26404; 39399</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83565; 101284</t>
+          <t>84016; 103017</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>120842; 140844</t>
+          <t>122182; 141093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>105818; 126188</t>
+          <t>106450; 125042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>61657; 78759</t>
+          <t>56280; 71456</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65410</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100418</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83288</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50837</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>49845</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>91857</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>89556</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>48068</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>65410</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100418</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83288</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>54862</t>
+          <t>42829</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>102930</t>
+          <t>93666</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42837; 57049</t>
+          <t>57509; 73069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84282; 98901</t>
+          <t>92635; 106883</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82414; 95323</t>
+          <t>74774; 91500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40945; 54779</t>
+          <t>42361; 57491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57399; 72638</t>
+          <t>42715; 56965</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92659; 107506</t>
+          <t>84948; 98411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74959; 91335</t>
+          <t>83029; 95538</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47325; 62850</t>
+          <t>35678; 48414</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>103475; 125600</t>
+          <t>104128; 124992</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182667; 203247</t>
+          <t>182166; 202710</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161066; 182803</t>
+          <t>161646; 182828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91529; 113288</t>
+          <t>82170; 103732</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42502</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>61785</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58604</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42305</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>41880</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>60542</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>54686</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69258</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42502</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61785</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58604</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46238</t>
+          <t>36623</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>78928</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35670; 48125</t>
+          <t>36222; 48849</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54030; 66245</t>
+          <t>54196; 68783</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47431; 60473</t>
+          <t>51961; 64976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56562; 83463</t>
+          <t>35485; 48334</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36637; 48652</t>
+          <t>35855; 47583</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54916; 68838</t>
+          <t>53005; 66248</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>51173; 63914</t>
+          <t>47788; 60356</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38167; 51950</t>
+          <t>29463; 43304</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>75751; 92591</t>
+          <t>74834; 92654</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112514; 131685</t>
+          <t>111477; 131507</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103453; 121575</t>
+          <t>104314; 122227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>101726; 136339</t>
+          <t>70088; 88340</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41657</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74458</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>66415</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38251</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50634</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>82508</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>76542</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30668</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41657</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74458</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66415</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40617</t>
+          <t>31556</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71285</t>
+          <t>69806</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42056; 57011</t>
+          <t>34746; 48772</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74334; 89584</t>
+          <t>66632; 82677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69399; 83086</t>
+          <t>58689; 71824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24433; 36307</t>
+          <t>32233; 44141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34954; 48111</t>
+          <t>43665; 57241</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66157; 82044</t>
+          <t>75105; 89661</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58712; 72248</t>
+          <t>68996; 83043</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33043; 46564</t>
+          <t>25411; 37269</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82965; 101613</t>
+          <t>82153; 102101</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>145715; 166773</t>
+          <t>144953; 166783</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131472; 151145</t>
+          <t>132219; 152735</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>61466; 79238</t>
+          <t>60919; 78072</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>434</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>214</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200999</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>304222</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>268476</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>162456</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>184301</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>299556</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>276814</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>180457</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>200999</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>304222</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>268476</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>179964</t>
+          <t>144687</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>360421</t>
+          <t>307143</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>171440; 198509</t>
+          <t>186230; 213697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>284619; 312540</t>
+          <t>289252; 319160</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>263178; 289108</t>
+          <t>254378; 281816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>163670; 205255</t>
+          <t>150383; 175572</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>188033; 215929</t>
+          <t>171439; 199853</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>287798; 318138</t>
+          <t>285815; 312603</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>254604; 282717</t>
+          <t>262174; 289089</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164795; 193078</t>
+          <t>131478; 155723</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>366403; 403945</t>
+          <t>364768; 404199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>582699; 623538</t>
+          <t>583210; 621768</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>526669; 564503</t>
+          <t>525292; 563262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>339051; 388210</t>
+          <t>289848; 326240</t>
         </is>
       </c>
     </row>
